--- a/stories/arbres/ATOM-JEU.REG.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Marceau et papa jouent au loto, à la table. Les cartons sont lisses. Marceau a envie de gagner. Papa pose sa dernière image. Papa a gagné. Marceau sent un nœud dans le ventre. Ses yeux piquent un peu. Papa dit : l'autre peut gagner. C'est le jeu. Marceau dit : je suis déçu. Papa dit : être déçu, c'est permis. Marceau souffle. Il dit : bravo papa. Papa sourit. Papa dit : on peut rejouer plus tard. Marceau hoche la tête. Plus tard, au jardin, maman joue aux quilles. Maman fait tomber les quilles. Maman a gagné. Marceau sent encore le nœud. Il dit : je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Il dit : bravo maman. Maman dit : on rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
+          <t>Marceau et papa jouent au loto, à la table. Les cartons sont lisses. Marceau a envie de gagner. Papa pose sa dernière image. Papa a gagné. Marceau sent un nœud dans le ventre. Ses yeux piquent un peu. L'autre peut gagner. C'est le jeu. Je suis déçu. Être déçu, c'est permis. Marceau souffle. Bravo papa. Papa sourit. On peut rejouer plus tard. Marceau hoche la tête. Plus tard, au jardin, maman joue aux quilles. Maman fait tomber les quilles. Maman a gagné. Marceau sent encore le nœud. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Bravo maman. On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,21 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau et papa jouent au loto, à la table. Les cartons sont lisses. Marceau a envie de gagner. Papa pose sa dernière image. Papa a gagné. Marceau sent un nœud dans le ventre. Ses yeux piquent un peu.
+papa|L'autre peut gagner. C'est le jeu.
+enfant-m|Je suis déçu.
+papa|Être déçu, c'est permis.
+narrateur|Marceau souffle.
+narrateur|Bravo papa. Papa sourit.
+papa|On peut rejouer plus tard.
+narrateur|Marceau hoche la tête. Plus tard, au jardin, maman joue aux quilles. Maman fait tomber les quilles. Maman a gagné. Marceau sent encore le nœud.
+narrateur|Je suis déçu. Être déçu, c'est permis. L'autre peut gagner.
+narrateur|Bravo maman.
+maman|On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a gagné. Que peut faire Marceau ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau range les quilles. Papa range le loto. Ils vont boire de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,7 @@
 maman|On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Papa a gagné. Que peut faire Marceau ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Marceau a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Marceau range les quilles. Papa range le loto. Ils vont boire de l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marceau dit bravo deux fois</t>
+          <t>Le loto de Victorino, puis les quilles</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino perd au loto, puis aux quilles. Deux fois il dit bravo. Ils rejoueront plus tard.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Marceau et papa jouent au loto, à la table. Les cartons sont lisses. Marceau a envie de gagner. Papa pose sa dernière image. Papa a gagné. Marceau sent un nœud dans le ventre. Ses yeux piquent un peu. L'autre peut gagner. C'est le jeu. Je suis déçu. Être déçu, c'est permis. Marceau souffle. Bravo papa. Papa sourit. On peut rejouer plus tard. Marceau hoche la tête. Plus tard, au jardin, maman joue aux quilles. Maman fait tomber les quilles. Maman a gagné. Marceau sent encore le nœud. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Bravo maman. On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
+          <t>Le rideau bouge un peu, tout seul. Des grains de soleil dansent dans l'air. Une boîte en métal cliquette sur la table. Dedans, les images du loto sont lisses. Ça sent le savon, près de la fenêtre. Un oiseau passe derrière le rideau. La table est lisse, un peu froide. Une image montre une poire jaune. Tu as vu les grains de soleil, Victorino ? Oui. Ils dansent. En ce moment, papa pose les cartons. Victorino pose une image, puis une autre. Elle est douce, papa. Oui. On cherche les images. Victorino a envie de gagner. Papa pose sa dernière image. J'ai fini. J'ai gagné ce tour. Victorino sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Victorino souffle. Le rideau bouge encore. Bravo papa. Merci. On peut rejouer plus tard. D'accord. Plus tard, au jardin, l'air sent la terre. Maman aligne des quilles sur l'herbe. On joue aux quilles, Victorino ? Oui, maman. Maman fait tomber les quilles. Elles sont tombées. J'ai gagné ce tour. Victorino sent encore le nœud. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Bravo maman. On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On dit bravo. Tu as dit bravo deux fois. Bravo, Victorino. C'est du bon travail. Un oiseau crie tout près, puis plus. On range les quilles ? Oui. Puis un peu d'eau. Victorino empile une quille, puis une autre. L'herbe pique un peu les genoux. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. C'est le jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Marceau et papa jouent au loto, à la table. Les cartons sont lisses. Marceau a envie de gagner. Papa pose sa dernière image. Papa a gagné. Marceau sent un nœud dans le ventre. Ses yeux piquent un peu.
-papa|L'autre peut gagner. C'est le jeu.
+          <t>narrateur|Le rideau bouge un peu, tout seul.
+narrateur|Des grains de soleil dansent dans l'air.
+narrateur|Une boîte en métal cliquette sur la table.
+narrateur|Dedans, les images du loto sont lisses.
+narrateur|Ça sent le savon, près de la fenêtre.
+narrateur|Un oiseau passe derrière le rideau.
+narrateur|La table est lisse, un peu froide.
+narrateur|Une image montre une poire jaune.
+papa|Tu as vu les grains de soleil, Victorino ?
+enfant-m|Oui. Ils dansent.
+narrateur|En ce moment, papa pose les cartons.
+narrateur|Victorino pose une image, puis une autre.
+enfant-m|Elle est douce, papa.
+papa|Oui. On cherche les images.
+narrateur|Victorino a envie de gagner.
+narrateur|Papa pose sa dernière image.
+papa|J'ai fini. J'ai gagné ce tour.
+narrateur|Victorino sent un nœud dans le ventre.
+narrateur|Ses yeux piquent un peu.
 enfant-m|Je suis déçu.
 papa|Être déçu, c'est permis.
-narrateur|Marceau souffle.
-narrateur|Bravo papa. Papa sourit.
-papa|On peut rejouer plus tard.
-narrateur|Marceau hoche la tête. Plus tard, au jardin, maman joue aux quilles. Maman fait tomber les quilles. Maman a gagné. Marceau sent encore le nœud.
-narrateur|Je suis déçu. Être déçu, c'est permis. L'autre peut gagner.
-narrateur|Bravo maman.
-maman|On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|L'autre peut gagner. C'est le jeu.
+narrateur|Victorino souffle. Le rideau bouge encore.
+enfant-m|Bravo papa.
+papa|Merci. On peut rejouer plus tard.
+enfant-m|D'accord.
+narrateur|Plus tard, au jardin, l'air sent la terre.
+narrateur|Maman aligne des quilles sur l'herbe.
+maman|On joue aux quilles, Victorino ?
+enfant-m|Oui, maman.
+narrateur|Maman fait tomber les quilles.
+maman|Elles sont tombées. J'ai gagné ce tour.
+narrateur|Victorino sent encore le nœud.
+enfant-m|Je suis déçu.
+maman|Être déçu, c'est permis.
+enfant-m|L'autre peut gagner.
+enfant-m|Bravo maman.
+maman|On rejoue plus tard.
+maman|Au salon, puis au jardin, c'est pareil.
+maman|Perdre, c'est le jeu. On dit bravo.
+papa|Tu as dit bravo deux fois.
+papa|Bravo, Victorino. C'est du bon travail.
+narrateur|Un oiseau crie tout près, puis plus.
+enfant-m|On range les quilles ?
+maman|Oui. Puis un peu d'eau.
+narrateur|Victorino empile une quille, puis une autre.
+narrateur|L'herbe pique un peu les genoux.
+papa|Tu as dit bravo. L'autre peut gagner.
+enfant-m|On rejoue plus tard.
+maman|Oui. C'est le jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa a gagné. Que peut faire Marceau ?</t>
+          <t>Papa a gagné. Que peut faire Victorino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,10 +1556,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa a gagné. Que peut faire Marceau ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Papa a gagné.
+narrateur|Que peut faire Victorino ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Marceau a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
+          <t>Victorino a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard. Tu as dit bravo au salon ? Oui. Et au jardin aussi. Bravo. L'autre peut gagner. C'est le jeu. Le rideau du salon ne bouge plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,10 +1728,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Marceau a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino a dit bravo.
+narrateur|Il était déçu, et c'était permis.
+narrateur|Ils rejoueront plus tard.
+papa|Tu as dit bravo au salon ?
+enfant-m|Oui. Et au jardin aussi.
+maman|Bravo. L'autre peut gagner. C'est le jeu.
+narrateur|Le rideau du salon ne bouge plus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,7 +1761,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Marceau range les quilles. Papa range le loto. Ils vont boire de l'eau.</t>
+          <t>Victorino range les quilles. Papa range le loto dans la boîte. On va boire de l'eau ? Oui. J'ai soif. L'eau est fraîche. Le nœud est plus petit. Être déçu, c'est permis. Plus tard, on rejoue. La boîte cliquette encore un peu. Victorino boit. L'eau coule froide.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,10 +1897,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Marceau range les quilles. Papa range le loto. Ils vont boire de l'eau.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorino range les quilles.
+narrateur|Papa range le loto dans la boîte.
+papa|On va boire de l'eau ?
+enfant-m|Oui. J'ai soif.
+maman|L'eau est fraîche.
+enfant-m|Le nœud est plus petit.
+maman|Être déçu, c'est permis.
+papa|Plus tard, on rejoue.
+narrateur|La boîte cliquette encore un peu.
+narrateur|Victorino boit. L'eau coule froide.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1933,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La boîte en métal est fermée. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Victorino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,10 +2073,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La boîte en métal est fermée.
+enfant-m|J'étais déçu. C'était permis.
+papa|Oui. Tu as dit bravo.
+maman|On rejoue plus tard.
+papa|Bravo, Victorino.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2137,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau bouge un peu, tout seul. Des grains de soleil dansent dans l'air. Une boîte en métal cliquette sur la table. Dedans, les images du loto sont lisses. Ça sent le savon, près de la fenêtre. Un oiseau passe derrière le rideau. La table est lisse, un peu froide. Une image montre une poire jaune. Tu as vu les grains de soleil, Victorino ? Oui. Ils dansent. En ce moment, papa pose les cartons. Victorino pose une image, puis une autre. Elle est douce, papa. Oui. On cherche les images. Victorino a envie de gagner. Papa pose sa dernière image. J'ai fini. J'ai gagné ce tour. Victorino sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Victorino souffle. Le rideau bouge encore. Bravo papa. Merci. On peut rejouer plus tard. D'accord. Plus tard, au jardin, l'air sent la terre. Maman aligne des quilles sur l'herbe. On joue aux quilles, Victorino ? Oui, maman. Maman fait tomber les quilles. Elles sont tombées. J'ai gagné ce tour. Victorino sent encore le nœud. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Bravo maman. On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On dit bravo. Tu as dit bravo deux fois. Bravo, Victorino. C'est du bon travail. Un oiseau crie tout près, puis plus. On range les quilles ? Oui. Puis un peu d'eau. Victorino empile une quille, puis une autre. L'herbe pique un peu les genoux. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. C'est le jeu.</t>
+          <t>Le rideau bouge un peu, tout seul. Des grains de soleil dansent dans l'air. Une boîte en métal cliquette sur la table. Dedans, les images du loto sont lisses. Ça sent le savon, près de la fenêtre. Un oiseau passe derrière le rideau. La table est lisse, un peu froide. Une image montre une poire jaune. Tu as vu les grains de soleil, Victorino ? Oui. Ils dansent. En ce moment, papa pose les cartons. Victorino pose une image, puis une autre. Elle est douce, papa. Oui. On cherche les images. Victorino a envie de gagner. Papa pose sa dernière image. J'ai fini. J'ai gagné ce tour. Victorino sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Victorino souffle. Le rideau bouge encore. Bravo papa. Merci. On peut rejouer plus tard. D'accord. Plus tard, au jardin, l'air sent la terre. Maman aligne des quilles sur l'herbe. On joue aux quilles, Victorino ? Oui, maman. Maman fait tomber les quilles. Elles sont tombées. J'ai gagné ce tour. Victorino sent encore le nœud. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Bravo maman. On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On dit bravo. Tu as dit bravo deux fois. Un oiseau crie tout près, puis plus. On range les quilles ? Oui. Puis un peu d'eau. Victorino empile une quille, puis une autre. L'herbe pique un peu les genoux. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. C'est le jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Marceau et papa jouent au loto, à la table. Les cartons sont lisses. Marceau a envie de gagner. Papa pose sa dernière image. Papa a gagné. Marceau sent un nœud dans le ventre. Ses yeux piquent un peu. Papa dit : &lt;emphasis level="moderate"&gt;l'autre&lt;/emphasis&gt; peut gagner. C'est le jeu. Marceau dit : je suis déçu. Papa dit : être déçu, c'est permis. Marceau souffle. Il dit : bravo papa. Papa sourit. Papa dit : on peut rejouer plus tard. Marceau hoche la tête. Plus tard, au jardin, maman joue aux quilles. Maman fait tomber les quilles. Maman a gagné. Marceau sent encore le nœud. Il dit : je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Il dit : bravo maman. Maman dit : on rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On peut être déçu. On dit bravo. On rejoue plus tard.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau bouge un peu, tout seul. Des grains de soleil dansent dans l'air. Une boîte en métal cliquette sur la table. Dedans, les images du loto sont lisses. Ça sent le savon, près de la fenêtre. Un oiseau passe derrière le rideau. La table est lisse, un peu froide. Une image montre une poire jaune. Tu as vu les grains de soleil, Victorino ? Oui. Ils dansent. En ce moment, papa pose les cartons. Victorino pose une image, puis une autre. Elle est douce, papa. Oui. On cherche les images. Victorino a envie de gagner. Papa pose sa dernière image. J'ai fini. J'ai gagné ce tour. Victorino sent un nœud dans le ventre. Ses yeux piquent un peu. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Victorino souffle. Le rideau bouge encore. Bravo papa. Merci. On peut rejouer plus tard. D'accord. Plus tard, au jardin, l'air sent la terre. Maman aligne des quilles sur l'herbe. On joue aux quilles, Victorino ? Oui, maman. Maman fait tomber les quilles. Elles sont tombées. J'ai gagné ce tour. Victorino sent encore le nœud. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. Bravo maman. On rejoue plus tard. Au salon, puis au jardin, c'est pareil. Perdre, c'est le jeu. On dit bravo. Tu as dit bravo deux fois. Un oiseau crie tout près, puis plus. On range les quilles ? Oui. Puis un peu d'eau. Victorino empile une quille, puis une autre. L'herbe pique un peu les genoux. Tu as dit bravo. L'autre peut gagner. On rejoue plus tard. Oui. C'est le jeu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 maman|Au salon, puis au jardin, c'est pareil.
 maman|Perdre, c'est le jeu. On dit bravo.
 papa|Tu as dit bravo deux fois.
-papa|Bravo, Victorino. C'est du bon travail.
 narrateur|Un oiseau crie tout près, puis plus.
 enfant-m|On range les quilles ?
 maman|Oui. Puis un peu d'eau.
@@ -1405,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa a gagné. Que peut faire Marceau ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a gagné. Que peut faire Victorino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1589,7 +1588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Marceau a dit bravo. Il était &lt;emphasis level="moderate"&gt;déçu&lt;/emphasis&gt;, et c'était permis. Ils rejoueront plus tard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a dit bravo. Il était déçu, et c'était permis. Ils rejoueront plus tard. Tu as dit bravo au salon ? Oui. Et au jardin aussi. Bravo. L'autre peut gagner. C'est le jeu. Le rideau du salon ne bouge plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1766,7 +1765,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Marceau range les quilles. Papa range le loto. Ils vont boire de l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino range les quilles. Papa range le loto dans la boîte. On va boire de l'eau ? Oui. J'ai soif. L'eau est fraîche. Le nœud est plus petit. Être déçu, c'est permis. Plus tard, on rejoue. La boîte cliquette encore un peu. Victorino boit. L'eau coule froide.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1933,12 +1932,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La boîte en métal est fermée. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Victorino. L'histoire est finie.</t>
+          <t>La boîte en métal est fermée. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La boîte en métal est fermée. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2077,8 +2076,7 @@
 enfant-m|J'étais déçu. C'était permis.
 papa|Oui. Tu as dit bravo.
 maman|On rejoue plus tard.
-papa|Bravo, Victorino.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Victorino.</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2144,6 +2142,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marceau, papa, maman</t>
+          <t>Victorino, papa, maman</t>
         </is>
       </c>
     </row>
